--- a/商業（しょうぎょう）.xlsx
+++ b/商業（しょうぎょう）.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="358">
   <si>
     <t>貨幣（かへい）</t>
   </si>
@@ -1620,6 +1620,15 @@
   </si>
   <si>
     <t>きんゆううきき</t>
+  </si>
+  <si>
+    <t>預金</t>
+  </si>
+  <si>
+    <t>よきん</t>
+  </si>
+  <si>
+    <t>存款</t>
   </si>
 </sst>
 </file>
@@ -3725,7 +3734,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:C25"/>
+  <dimension ref="A2:C26"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="18.6666666666667" customWidth="1"/>
@@ -3968,6 +3977,17 @@
         <v>354</v>
       </c>
     </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>355</v>
+      </c>
+      <c r="B26" t="s">
+        <v>356</v>
+      </c>
+      <c r="C26" t="s">
+        <v>357</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/商業（しょうぎょう）.xlsx
+++ b/商業（しょうぎょう）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="5"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="基礎「きそ」" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="367">
   <si>
     <t>貨幣（かへい）</t>
   </si>
@@ -791,10 +791,25 @@
     <t>しほん</t>
   </si>
   <si>
+    <t>売り切れ</t>
+  </si>
+  <si>
+    <t>うりきれ</t>
+  </si>
+  <si>
+    <t>（售罄）</t>
+  </si>
+  <si>
     <t>費用</t>
   </si>
   <si>
     <t>ひよう</t>
+  </si>
+  <si>
+    <t>客席</t>
+  </si>
+  <si>
+    <t>きゃくせき</t>
   </si>
   <si>
     <t>宣伝費用</t>
@@ -1433,6 +1448,12 @@
     <t>よしのや</t>
   </si>
   <si>
+    <t>屋外広告物</t>
+  </si>
+  <si>
+    <t>おくがいこうこくぶつ</t>
+  </si>
+  <si>
     <t>含み益</t>
   </si>
   <si>
@@ -1629,6 +1650,12 @@
   </si>
   <si>
     <t>存款</t>
+  </si>
+  <si>
+    <t>資本主義</t>
+  </si>
+  <si>
+    <t>しほんしゅぎ</t>
   </si>
 </sst>
 </file>
@@ -3057,183 +3084,198 @@
       </c>
     </row>
     <row r="22" spans="5:11">
+      <c r="E22" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>137</v>
+      </c>
       <c r="I22" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="5:11">
+      <c r="E23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="I23" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="5:11">
       <c r="I24" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="5:11">
       <c r="I25" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="5:11">
       <c r="I26" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="5:11">
       <c r="I27" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="5:11">
       <c r="I28" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" spans="5:11">
       <c r="I29" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="5:11">
       <c r="I30" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="5:11">
       <c r="I31" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="5:11">
       <c r="I32" s="1" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="9:13">
       <c r="I33" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="9:13">
       <c r="I34" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" spans="9:13">
       <c r="I35" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="9:13">
       <c r="I36" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="9:13">
       <c r="I37" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="9:13">
       <c r="I38" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="39" spans="9:13">
       <c r="I39" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -3254,72 +3296,72 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C5" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="C6" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
@@ -3340,29 +3382,29 @@
     </row>
     <row r="12" ht="18" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -3383,146 +3425,146 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -3543,166 +3585,166 @@
   <sheetData>
     <row r="2" ht="18" spans="1:6">
       <c r="A2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:6">
       <c r="A3" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C4" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -3714,15 +3756,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="1" outlineLevelCol="1"/>
+  <dimension ref="A2:B3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="2" outlineLevelCol="1"/>
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>291</v>
+        <v>296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B3" t="s">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -3734,7 +3784,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:C26"/>
+  <dimension ref="A2:C27"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="13.8" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="18.6666666666667" customWidth="1"/>
@@ -3742,250 +3792,258 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B2" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B3" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B4" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B5" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="B6" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C6" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B7" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B8" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C8" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="B9" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C9" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B10" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="C10" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B11" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="C11" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B12" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="C12" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="B13" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C13" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="B14" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C14" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B15" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="C15" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B16" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C16" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B17" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="C17" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B18" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="C18" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B19" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C19" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B20" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="C20" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B21" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C21" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B22" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B23" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="B24" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B25" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="B26" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C26" t="s">
-        <v>357</v>
+        <v>364</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>365</v>
+      </c>
+      <c r="B27" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/商業（しょうぎょう）.xlsx
+++ b/商業（しょうぎょう）.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="370">
   <si>
     <t>貨幣（かへい）</t>
   </si>
@@ -1076,6 +1076,15 @@
       </rPr>
       <t>假货）</t>
     </r>
+  </si>
+  <si>
+    <t>値下り</t>
+  </si>
+  <si>
+    <t>ねさがり</t>
+  </si>
+  <si>
+    <t>（跌价）</t>
   </si>
   <si>
     <t>写真</t>
@@ -2617,7 +2626,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="13.8888888888889" style="1" customWidth="1"/>
@@ -3278,6 +3287,17 @@
         <v>187</v>
       </c>
     </row>
+    <row r="40" spans="9:13">
+      <c r="I40" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>190</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -3296,72 +3316,72 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C5" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C6" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
@@ -3382,29 +3402,29 @@
     </row>
     <row r="12" ht="18" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -3425,146 +3445,146 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -3585,166 +3605,166 @@
   <sheetData>
     <row r="2" ht="18" spans="1:6">
       <c r="A2" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:6">
       <c r="A3" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -3761,18 +3781,18 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -3792,258 +3812,258 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B3" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B4" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B6" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B7" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B8" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C8" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B9" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C9" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B10" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C10" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B11" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C11" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B12" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C12" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B13" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C13" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B14" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C14" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B15" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C15" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B16" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C16" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B17" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C17" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B18" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C18" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B19" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C19" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B20" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C20" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B21" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C21" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B22" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B23" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B24" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B25" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B26" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C26" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B27" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/商業（しょうぎょう）.xlsx
+++ b/商業（しょうぎょう）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="基礎「きそ」" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="373">
   <si>
     <t>貨幣（かへい）</t>
   </si>
@@ -1085,6 +1085,15 @@
   </si>
   <si>
     <t>（跌价）</t>
+  </si>
+  <si>
+    <t>割り引く</t>
+  </si>
+  <si>
+    <t>わりびく</t>
+  </si>
+  <si>
+    <t>（减价）</t>
   </si>
   <si>
     <t>写真</t>
@@ -2626,7 +2635,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="2" width="13.8888888888889" style="1" customWidth="1"/>
@@ -3298,6 +3307,17 @@
         <v>190</v>
       </c>
     </row>
+    <row r="41" spans="9:13">
+      <c r="I41" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -3316,72 +3336,72 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
@@ -3402,29 +3422,29 @@
     </row>
     <row r="12" ht="18" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3445,146 +3465,146 @@
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -3605,166 +3625,166 @@
   <sheetData>
     <row r="2" ht="18" spans="1:6">
       <c r="A2" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:6">
       <c r="A3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C4" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:6">
       <c r="A7" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:6">
       <c r="A8" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:6">
       <c r="A10" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:6">
       <c r="A11" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:6">
       <c r="A12" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:6">
       <c r="A13" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:6">
       <c r="A14" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:6">
       <c r="A15" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -3781,18 +3801,18 @@
   <sheetData>
     <row r="2" ht="18" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -3812,258 +3832,258 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B5" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B6" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B8" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C8" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B9" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B10" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C10" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B11" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C11" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B12" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C12" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B13" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C13" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B14" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C14" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B15" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C15" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B16" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C16" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B17" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C17" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B18" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C18" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B19" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C19" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B20" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C20" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B21" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C21" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B22" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B23" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B24" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B25" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B26" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C26" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B27" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
